--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,26 +515,26 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -556,99 +556,99 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -660,47 +660,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,52 +712,104 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -772,12 +824,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -829,25 +881,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>K. Domingues | S. Sousa</t>
+          <t>S. Sousa | T. Filipe</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54.3</v>
+        <v>81.8</v>
       </c>
       <c r="E2" t="n">
-        <v>55.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -858,7 +910,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -867,16 +919,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50.9</v>
+        <v>81.8</v>
       </c>
       <c r="E3" t="n">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -887,25 +939,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best net</t>
+          <t>Best defense</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S. Sousa | T. Filipe</t>
+          <t>M. Sousa | S. Sousa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50.9</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>71.5</v>
+        <v>66.8</v>
       </c>
       <c r="F4" t="n">
-        <v>64.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="G4" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>K. Domingues | M. Sousa | S. Sousa</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>65</v>
+      </c>
+      <c r="E5" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -1135,16 +1216,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="3">
@@ -1154,16 +1235,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.9</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="4">
@@ -1173,16 +1254,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="5">
@@ -1192,16 +1273,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-9.6</v>
+        <v>-5.8</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="6">
@@ -1211,16 +1292,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.5</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="7">
@@ -1230,7 +1311,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
@@ -1255,10 +1336,10 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1268,16 +1349,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -1293,10 +1374,10 @@
         <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1312,7 +1393,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1380,7 +1461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1470,7 +1551,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Finish possessions: the first stop is not enough against this team because the offensive glass is a real source of extra points.</t>
+          <t>Know the first reference: S. Sousa is a inside scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1482,19 +1563,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Know the first reference: S. Sousa is a primary scorer, and the plan should start with taking away his comfort.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Game Plan Keys</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Closeout discipline matters: S. Sousa are the first perimeter names you cannot lose in help situations.</t>
+          <t>Closeout discipline matters: M. Sousa, S. Sousa are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1536,7 +1605,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The main offensive references are S. Sousa and K. Domingues; load the scouting plan into those names first.</t>
+          <t>The main offensive references are S. Sousa and T. Filipe; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1617,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with S. Sousa; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with M. Sousa, S. Sousa, and J. Mendes; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1629,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from J. Mendes and T. Filipe; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from T. Filipe and W. Oliveira; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1608,19 +1677,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondary lineup to recognize: J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe.</t>
+          <t>Recognize the main duo/trio combinations: S. Sousa | T. Filipe and S. Sousa | T. Filipe.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Defensive Emphasis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: K. Domingues | S. Sousa and S. Sousa | T. Filipe.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>
@@ -1632,19 +1701,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Defensive Emphasis</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Do not lose S. Sousa in help-and-recover situations.</t>
+          <t>Do not lose M. Sousa and S. Sousa in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1726,53 +1783,53 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1789,108 +1846,144 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.9</v>
+        <v>29.1</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.5</v>
+        <v>27.9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>bench spacer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2004,36 +2097,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2045,41 +2138,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_S._SOUSA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>S. Sousa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2091,41 +2184,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2137,37 +2230,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SLB_W._OLIVEIRA</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>W. Oliveira</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2188,36 +2281,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SLB_G._TE</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G. Te</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2229,74 +2322,94 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>38</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>42.1%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>34.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>28</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>21.4%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>25.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SLB_G._TE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>G. Te</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2314,23 +2427,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
     </row>
@@ -2350,23 +2463,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -2386,42 +2499,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SLB_T._FILIPE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>T. Filipe</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2430,15 +2535,15 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2446,26 +2551,18 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SLB_S._SOUSA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>S. Sousa</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2474,23 +2571,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2599,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2522,19 +2619,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2643,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_S._SOUSA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>S. Sousa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2562,23 +2659,199 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>13</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>28.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SLB_K._DOMINGUES</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>K. Domingues</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>63.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SLB_J._MENDES</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>J. Mendes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>7</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>0.9</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>38.9%</t>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SLB_M._SOUSA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M. Sousa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>31.6%</t>
         </is>
       </c>
     </row>
@@ -2593,10 +2866,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -2648,40 +2921,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>29.1</v>
       </c>
       <c r="D2" t="n">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="E2" t="n">
-        <v>78.3</v>
+        <v>71.5</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Best defense</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>J. Mendes | K. Domingues | M. Sousa | S. Sousa | T. Filipe</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>
